--- a/artfynd/A 8676-2020 artfynd.xlsx
+++ b/artfynd/A 8676-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8676-2020 artfynd.xlsx
+++ b/artfynd/A 8676-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2619,141 +2619,6 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16856166</v>
-      </c>
-      <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Gladtjärnen OSO (knärot), Vstm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>554809.6066502887</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6636343.129368551</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Fagersta</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Västervåla</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>U-Fag-0140</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2014-10-27</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2014-10-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Koord: 1509718/6637976/10m. Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Einar Marklund</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
